--- a/data/dividends_info_20260629.xlsx
+++ b/data/dividends_info_20260629.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>64.37999725341797</v>
+        <v>63.58000183105469</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1397949733451128</v>
+        <v>0.1415539437056777</v>
       </c>
       <c r="J2" t="n">
         <v>259</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>64.40000152587891</v>
+        <v>64.09999847412109</v>
       </c>
       <c r="I3" t="n">
-        <v>1.086956495985031</v>
+        <v>1.092043707743002</v>
       </c>
       <c r="J3" t="n">
         <v>238</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9.399999618530273</v>
+        <v>9.380000114440918</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6382978982437579</v>
+        <v>0.6396588408098992</v>
       </c>
       <c r="J4" t="n">
         <v>168</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>64.37999725341797</v>
+        <v>63.58000183105469</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1397949733451128</v>
+        <v>0.1415539437056777</v>
       </c>
       <c r="J6" t="n">
         <v>168</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>20.5049991607666</v>
+        <v>20.5</v>
       </c>
       <c r="I8" t="n">
-        <v>1.316752065596797</v>
+        <v>1.317073170731707</v>
       </c>
       <c r="J8" t="n">
         <v>147</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5.880000114440918</v>
+        <v>5.829999923706055</v>
       </c>
       <c r="I9" t="n">
-        <v>3.401360478017889</v>
+        <v>3.430531777311974</v>
       </c>
       <c r="J9" t="n">
         <v>140</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5.900000095367432</v>
+        <v>5.840000152587891</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8474576134203634</v>
+        <v>0.8561643611917271</v>
       </c>
       <c r="J12" t="n">
         <v>98</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>4.989999771118164</v>
+        <v>4.980000019073486</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7615230810218038</v>
+        <v>0.7630522059128382</v>
       </c>
       <c r="J13" t="n">
         <v>91</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>20.5049991607666</v>
+        <v>20.5</v>
       </c>
       <c r="I14" t="n">
-        <v>1.316752065596797</v>
+        <v>1.317073170731707</v>
       </c>
       <c r="J14" t="n">
         <v>84</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>64.37999725341797</v>
+        <v>63.58000183105469</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1397949733451128</v>
+        <v>0.1415539437056777</v>
       </c>
       <c r="J15" t="n">
         <v>84</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>6.019999980926514</v>
+        <v>6.039999961853027</v>
       </c>
       <c r="I16" t="n">
-        <v>4.983388720108072</v>
+        <v>4.966887448588033</v>
       </c>
       <c r="J16" t="n">
         <v>77</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>4.989999771118164</v>
+        <v>4.980000019073486</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7615230810218038</v>
+        <v>0.7630522059128382</v>
       </c>
       <c r="J18" t="n">
         <v>35</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>5.53000020980835</v>
+        <v>5.539999961853027</v>
       </c>
       <c r="I19" t="n">
-        <v>4.520795488517063</v>
+        <v>4.512635410134184</v>
       </c>
       <c r="J19" t="n">
         <v>28</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>10.10599994659424</v>
+        <v>10.10200023651123</v>
       </c>
       <c r="I21" t="n">
-        <v>2.572729085434253</v>
+        <v>2.573747712460875</v>
       </c>
       <c r="J21" t="n">
         <v>21</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>14.97999954223633</v>
+        <v>14.5600004196167</v>
       </c>
       <c r="I22" t="n">
-        <v>4.005340576335073</v>
+        <v>4.120879002116096</v>
       </c>
       <c r="J22" t="n">
         <v>21</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>2.839999914169312</v>
+        <v>2.822000026702881</v>
       </c>
       <c r="I23" t="n">
-        <v>7.746479107354097</v>
+        <v>7.795889366345604</v>
       </c>
       <c r="J23" t="n">
         <v>21</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>6.590000152587891</v>
+        <v>6.545000076293945</v>
       </c>
       <c r="I25" t="n">
-        <v>3.641881554520937</v>
+        <v>3.666921271235463</v>
       </c>
       <c r="J25" t="n">
         <v>21</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>18.70000076293945</v>
+        <v>18.75</v>
       </c>
       <c r="I26" t="n">
-        <v>2.010695105131624</v>
+        <v>2.005333333333333</v>
       </c>
       <c r="J26" t="n">
         <v>21</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>3.099999904632568</v>
+        <v>3.059999942779541</v>
       </c>
       <c r="I29" t="n">
-        <v>4.838709826275912</v>
+        <v>4.901960875977926</v>
       </c>
       <c r="J29" t="n">
         <v>14</v>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>2.279999971389771</v>
+        <v>2.259999990463257</v>
       </c>
       <c r="I30" t="n">
-        <v>3.728070222219713</v>
+        <v>3.761061962773576</v>
       </c>
       <c r="J30" t="n">
         <v>7</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>34.84999847412109</v>
+        <v>34.65000152587891</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4304160877119894</v>
+        <v>0.4329004138368366</v>
       </c>
       <c r="J32" t="n">
         <v>7</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>21.95999908447266</v>
+        <v>21.55999946594238</v>
       </c>
       <c r="I34" t="n">
-        <v>1.138433562944766</v>
+        <v>1.159554759706357</v>
       </c>
       <c r="J34" t="n">
         <v>-7</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>30.54999923706055</v>
+        <v>29.89999961853027</v>
       </c>
       <c r="I35" t="n">
-        <v>0.6382978882809376</v>
+        <v>0.6521739213640337</v>
       </c>
       <c r="J35" t="n">
         <v>-7</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>5.159999847412109</v>
+        <v>5.15500020980835</v>
       </c>
       <c r="I37" t="n">
-        <v>5.620155204954966</v>
+        <v>5.62560597860347</v>
       </c>
       <c r="J37" t="n">
         <v>-7</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>3.657999992370605</v>
+        <v>3.667999982833862</v>
       </c>
       <c r="I38" t="n">
-        <v>4.373974858767299</v>
+        <v>4.362050183991154</v>
       </c>
       <c r="J38" t="n">
         <v>-7</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>2.48799991607666</v>
+        <v>2.467999935150146</v>
       </c>
       <c r="I39" t="n">
-        <v>5.57073973774722</v>
+        <v>5.615883453885421</v>
       </c>
       <c r="J39" t="n">
         <v>-7</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>45.94499969482422</v>
+        <v>46.06000137329102</v>
       </c>
       <c r="I40" t="n">
-        <v>1.371204710381074</v>
+        <v>1.367781114234444</v>
       </c>
       <c r="J40" t="n">
         <v>-7</v>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>6.125</v>
+        <v>6.079999923706055</v>
       </c>
       <c r="I41" t="n">
-        <v>2.285714285714286</v>
+        <v>2.302631607841587</v>
       </c>
       <c r="J41" t="n">
         <v>-7</v>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>16.54999923706055</v>
+        <v>16.64999961853027</v>
       </c>
       <c r="I42" t="n">
-        <v>4.712991153820356</v>
+        <v>4.684684792015942</v>
       </c>
       <c r="J42" t="n">
         <v>-7</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>28.45999908447266</v>
+        <v>28.55999946594238</v>
       </c>
       <c r="I43" t="n">
-        <v>2.986648022992197</v>
+        <v>2.97619053184374</v>
       </c>
       <c r="J43" t="n">
         <v>-7</v>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>64.37999725341797</v>
+        <v>63.58000183105469</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1397949733451128</v>
+        <v>0.1415539437056777</v>
       </c>
       <c r="J44" t="n">
         <v>-7</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>1.379999995231628</v>
+        <v>1.399999976158142</v>
       </c>
       <c r="I45" t="n">
-        <v>0.7246376836632911</v>
+        <v>0.7142857264499277</v>
       </c>
       <c r="J45" t="n">
         <v>-7</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>6.323999881744385</v>
+        <v>6.329999923706055</v>
       </c>
       <c r="I46" t="n">
-        <v>2.866856473596122</v>
+        <v>2.864139055057894</v>
       </c>
       <c r="J46" t="n">
         <v>-7</v>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>8.739999771118164</v>
+        <v>8.729999542236328</v>
       </c>
       <c r="I47" t="n">
-        <v>2.974828453190412</v>
+        <v>2.978236124092589</v>
       </c>
       <c r="J47" t="n">
         <v>-7</v>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>10.31999969482422</v>
+        <v>10.27999973297119</v>
       </c>
       <c r="I48" t="n">
-        <v>2.684108606504355</v>
+        <v>2.694552599175406</v>
       </c>
       <c r="J48" t="n">
         <v>-7</v>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>0.9720000028610229</v>
+        <v>0.984000027179718</v>
       </c>
       <c r="I49" t="n">
-        <v>1.388888884800779</v>
+        <v>1.37195118161662</v>
       </c>
       <c r="J49" t="n">
         <v>-14</v>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>3.009999990463257</v>
+        <v>2.996000051498413</v>
       </c>
       <c r="I50" t="n">
-        <v>3.654485061412586</v>
+        <v>3.67156201966635</v>
       </c>
       <c r="J50" t="n">
         <v>-14</v>
@@ -2826,10 +2826,10 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>2.200000047683716</v>
+        <v>1.850000023841858</v>
       </c>
       <c r="I51" t="n">
-        <v>1.090909067264274</v>
+        <v>1.297297280578391</v>
       </c>
       <c r="J51" t="n">
         <v>-14</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>2.990000009536743</v>
+        <v>2.950000047683716</v>
       </c>
       <c r="I52" t="n">
-        <v>5.351170551494067</v>
+        <v>5.423728725890325</v>
       </c>
       <c r="J52" t="n">
         <v>-21</v>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>27.75</v>
+        <v>27.64999961853027</v>
       </c>
       <c r="I54" t="n">
-        <v>4</v>
+        <v>4.014466601497197</v>
       </c>
       <c r="J54" t="n">
         <v>-25</v>
@@ -3014,10 +3014,10 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>0.875</v>
+        <v>0.8659999966621399</v>
       </c>
       <c r="I55" t="n">
-        <v>3.428571428571429</v>
+        <v>3.464203246608575</v>
       </c>
       <c r="J55" t="n">
         <v>-28</v>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>0.4679999947547913</v>
+        <v>0.4589999914169312</v>
       </c>
       <c r="I56" t="n">
-        <v>4.914529969610546</v>
+        <v>5.010893339888545</v>
       </c>
       <c r="J56" t="n">
         <v>-28</v>
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>19.35000038146973</v>
+        <v>19.60000038146973</v>
       </c>
       <c r="I57" t="n">
-        <v>3.100775132669155</v>
+        <v>3.061224430216099</v>
       </c>
       <c r="J57" t="n">
         <v>-28</v>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>8.819999694824219</v>
+        <v>8.979999542236328</v>
       </c>
       <c r="I58" t="n">
-        <v>2.26757377460415</v>
+        <v>2.227171605736999</v>
       </c>
       <c r="J58" t="n">
         <v>-28</v>
@@ -5364,605 +5364,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Acinque S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Ariston Holding N.V.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Ariston Holding N.V.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>BREMBO N.V.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Banca Generali S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Cementir Holding N.V.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Cyberoo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Datrix S.p.A.</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Half Year Preliminary Results</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Davide Campari-Milano N.V.</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Davide Campari-Milano N.V.</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Dexelance S.p.A.</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>EDISON S.p.A.</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Enervit S.p.A.</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Eni S.p.A.</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>FINCANTIERI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Farmacosmo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>FinecoBank S.p.A.</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>GEOX S.p.A.</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>GEOX S.p.A.</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>HERA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>INWIT S.p.A.</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>ITALMOBILIARE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Lottomatica Group S.p.A.</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Nexi S.p.A.</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Prysmian S.p.A.</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>RECORDATI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Snam S.p.A.</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Snam S.p.A.</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>TELECOM ITALIA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>TERNA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>TERNA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>WEBUILD S.p.A.</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>